--- a/src/data/tables/Product_FAQs.xlsx
+++ b/src/data/tables/Product_FAQs.xlsx
@@ -225,7 +225,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,22 +234,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -744,151 +740,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1416,258 +1409,253 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="1"/>
-  <cols>
-    <col min="1" max="1" width="35.7403846153846" style="1" customWidth="1"/>
-    <col min="2" max="2" width="111.413461538462" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="14" style="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="18" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="185" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="269" spans="1:2">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="353" spans="1:2">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="336" spans="1:2">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="202" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="404" spans="1:2">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="236" spans="1:2">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="202" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="202" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="409.5" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="409.5" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A13" s="4" t="s">
+    <row r="13" ht="303" spans="1:2">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="101" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A15" s="3" t="s">
+    <row r="15" ht="409.5" spans="1:2">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="202" spans="1:2">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="409.5" spans="1:2">
+      <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A18" s="4" t="s">
+    <row r="18" ht="202" spans="1:2">
+      <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="409.5" spans="1:2">
+      <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A20" s="4" t="s">
+    <row r="20" ht="409.5" spans="1:2">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A21" s="3" t="s">
+    <row r="21" ht="168" spans="1:2">
+      <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A22" s="3" t="s">
+    <row r="22" ht="252" spans="1:2">
+      <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A23" s="3" t="s">
+    <row r="23" ht="336" spans="1:2">
+      <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A24" s="3" t="s">
+    <row r="24" ht="219" spans="1:2">
+      <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A25" s="4" t="s">
+    <row r="25" ht="409.5" spans="1:2">
+      <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A26" s="3" t="s">
+    <row r="26" ht="152" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A27" s="4" t="s">
+    <row r="27" ht="336" spans="1:2">
+      <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A28" s="3" t="s">
+    <row r="28" ht="236" spans="1:2">
+      <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A29" s="3" t="s">
+    <row r="29" ht="353" spans="1:2">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A30" s="3" t="s">
+    <row r="30" ht="269" spans="1:2">
+      <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A31" s="4" t="s">
+    <row r="31" ht="370" spans="1:2">
+      <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
     </row>
